--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,322 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121561250</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57466</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>625108</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7209511</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121561251</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>625210</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7209469</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121561249</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gunnarn, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>625237</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7209648</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561250</v>
+        <v>121561251</v>
       </c>
       <c r="B20" t="n">
-        <v>57466</v>
+        <v>57355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,20 +2711,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2733,16 +2733,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625108</v>
+        <v>625210</v>
       </c>
       <c r="R20" t="n">
-        <v>7209511</v>
+        <v>7209469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561251</v>
+        <v>121561250</v>
       </c>
       <c r="B21" t="n">
-        <v>57355</v>
+        <v>57466</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2813,20 +2818,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2835,21 +2840,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625210</v>
+        <v>625108</v>
       </c>
       <c r="R21" t="n">
-        <v>7209469</v>
+        <v>7209511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561251</v>
+        <v>121561249</v>
       </c>
       <c r="B20" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625237</v>
       </c>
       <c r="R20" t="n">
-        <v>7209469</v>
+        <v>7209648</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561250</v>
+        <v>121561251</v>
       </c>
       <c r="B21" t="n">
-        <v>57466</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2818,20 +2818,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2840,16 +2840,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625108</v>
+        <v>625210</v>
       </c>
       <c r="R21" t="n">
-        <v>7209511</v>
+        <v>7209469</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2908,10 +2913,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561249</v>
+        <v>121561250</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>57467</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2920,20 +2925,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2942,21 +2947,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625237</v>
+        <v>625108</v>
       </c>
       <c r="R22" t="n">
-        <v>7209648</v>
+        <v>7209511</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -2699,7 +2699,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561249</v>
+        <v>121561251</v>
       </c>
       <c r="B20" t="n">
         <v>57356</v>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625237</v>
+        <v>625210</v>
       </c>
       <c r="R20" t="n">
-        <v>7209648</v>
+        <v>7209469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561251</v>
+        <v>121561250</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2818,20 +2818,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2840,21 +2840,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625210</v>
+        <v>625108</v>
       </c>
       <c r="R21" t="n">
-        <v>7209469</v>
+        <v>7209511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2913,10 +2908,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561250</v>
+        <v>121561249</v>
       </c>
       <c r="B22" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2925,20 +2920,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2947,16 +2942,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625108</v>
+        <v>625237</v>
       </c>
       <c r="R22" t="n">
-        <v>7209511</v>
+        <v>7209648</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561251</v>
+        <v>121561250</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,20 +2711,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2733,21 +2733,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625108</v>
       </c>
       <c r="R20" t="n">
-        <v>7209469</v>
+        <v>7209511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561250</v>
+        <v>121561249</v>
       </c>
       <c r="B21" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2818,20 +2813,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2840,16 +2835,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625108</v>
+        <v>625237</v>
       </c>
       <c r="R21" t="n">
-        <v>7209511</v>
+        <v>7209648</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561249</v>
+        <v>121561251</v>
       </c>
       <c r="B22" t="n">
         <v>57356</v>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625237</v>
+        <v>625210</v>
       </c>
       <c r="R22" t="n">
-        <v>7209648</v>
+        <v>7209469</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561250</v>
+        <v>121561249</v>
       </c>
       <c r="B20" t="n">
-        <v>57467</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,20 +2711,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2733,16 +2733,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625108</v>
+        <v>625237</v>
       </c>
       <c r="R20" t="n">
-        <v>7209511</v>
+        <v>7209648</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561249</v>
+        <v>121561250</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57467</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2813,20 +2818,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2835,21 +2840,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625237</v>
+        <v>625108</v>
       </c>
       <c r="R21" t="n">
-        <v>7209648</v>
+        <v>7209511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561251</v>
+        <v>121561250</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,20 +2711,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2733,21 +2733,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625108</v>
       </c>
       <c r="R20" t="n">
-        <v>7209469</v>
+        <v>7209511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2913,10 +2908,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561250</v>
+        <v>121561251</v>
       </c>
       <c r="B22" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2925,20 +2920,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2947,16 +2942,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625108</v>
+        <v>625210</v>
       </c>
       <c r="R22" t="n">
-        <v>7209511</v>
+        <v>7209469</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -2699,10 +2699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561250</v>
+        <v>121561249</v>
       </c>
       <c r="B20" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,20 +2711,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2733,16 +2733,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625108</v>
+        <v>625237</v>
       </c>
       <c r="R20" t="n">
-        <v>7209511</v>
+        <v>7209648</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561249</v>
+        <v>121561250</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2813,20 +2818,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2835,21 +2840,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625237</v>
+        <v>625108</v>
       </c>
       <c r="R21" t="n">
-        <v>7209648</v>
+        <v>7209511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -2699,7 +2699,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561249</v>
+        <v>121561251</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625237</v>
+        <v>625210</v>
       </c>
       <c r="R20" t="n">
-        <v>7209648</v>
+        <v>7209469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561250</v>
+        <v>121561249</v>
       </c>
       <c r="B21" t="n">
-        <v>57468</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2818,20 +2818,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2840,16 +2840,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625108</v>
+        <v>625237</v>
       </c>
       <c r="R21" t="n">
-        <v>7209511</v>
+        <v>7209648</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2908,10 +2913,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561251</v>
+        <v>121561250</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
+        <v>57468</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2920,20 +2925,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2942,21 +2947,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625210</v>
+        <v>625108</v>
       </c>
       <c r="R22" t="n">
-        <v>7209469</v>
+        <v>7209511</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -2699,7 +2699,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561251</v>
+        <v>121561249</v>
       </c>
       <c r="B20" t="n">
         <v>57357</v>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625210</v>
+        <v>625237</v>
       </c>
       <c r="R20" t="n">
-        <v>7209469</v>
+        <v>7209648</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561249</v>
+        <v>121561251</v>
       </c>
       <c r="B21" t="n">
         <v>57357</v>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625237</v>
+        <v>625210</v>
       </c>
       <c r="R21" t="n">
-        <v>7209648</v>
+        <v>7209469</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 40652-2021 artfynd.xlsx
+++ b/artfynd/A 40652-2021 artfynd.xlsx
@@ -675,50 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111396323</v>
+        <v>111396308</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>625301.6605433678</v>
+        <v>625152</v>
       </c>
       <c r="R2" t="n">
-        <v>7209610.70454926</v>
+        <v>7209568</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +751,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,50 +780,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111396309</v>
+        <v>121561249</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Lill-Tjickuträsket, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>625341.71034419</v>
+        <v>625237</v>
       </c>
       <c r="R3" t="n">
-        <v>7209536.108963673</v>
+        <v>7209648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,50 +882,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111396312</v>
+        <v>121561251</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Lill-Tjickuträsket, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625242.7087276473</v>
+        <v>625210</v>
       </c>
       <c r="R4" t="n">
-        <v>7209468.80281719</v>
+        <v>7209469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,50 +984,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111396311</v>
+        <v>121561250</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V Lill-Tjickuträsket, Ly lm</t>
+          <t>Gunnarn, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625271.0561409625</v>
+        <v>625108</v>
       </c>
       <c r="R5" t="n">
-        <v>7209511.101565193</v>
+        <v>7209511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1081,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111396324</v>
+        <v>111396309</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625335.6676841485</v>
+        <v>625342</v>
       </c>
       <c r="R6" t="n">
-        <v>7209609.168182318</v>
+        <v>7209537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1149,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111396325</v>
+        <v>111396310</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>625389.9085714296</v>
+        <v>625289</v>
       </c>
       <c r="R7" t="n">
-        <v>7209580.514361567</v>
+        <v>7209519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1246,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1275,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111396313</v>
+        <v>111396311</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1310,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>625231.5510770321</v>
+        <v>625271</v>
       </c>
       <c r="R8" t="n">
-        <v>7209481.895207534</v>
+        <v>7209512</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1343,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111396318</v>
+        <v>111396312</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,10 +1407,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>625177.6865340136</v>
+        <v>625242</v>
       </c>
       <c r="R9" t="n">
-        <v>7209552.099144561</v>
+        <v>7209469</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1440,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111396319</v>
+        <v>111396313</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>625228.8129008666</v>
+        <v>625232</v>
       </c>
       <c r="R10" t="n">
-        <v>7209607.642547456</v>
+        <v>7209482</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1537,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111396316</v>
+        <v>111396314</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>625153.7279882778</v>
+        <v>625202</v>
       </c>
       <c r="R11" t="n">
-        <v>7209526.513740451</v>
+        <v>7209540</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1634,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111396310</v>
+        <v>111396315</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,10 +1698,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>625289.0018867656</v>
+        <v>625168</v>
       </c>
       <c r="R12" t="n">
-        <v>7209518.212698339</v>
+        <v>7209531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1731,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111396317</v>
+        <v>111396316</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1795,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>625153.5624699651</v>
+        <v>625154</v>
       </c>
       <c r="R13" t="n">
-        <v>7209550.662191558</v>
+        <v>7209527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1828,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111396322</v>
+        <v>111396317</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,10 +1892,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>625269.4478252844</v>
+        <v>625153</v>
       </c>
       <c r="R14" t="n">
-        <v>7209630.115016816</v>
+        <v>7209551</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1925,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1954,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111396315</v>
+        <v>111396318</v>
       </c>
       <c r="B15" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +1989,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>625167.9685939638</v>
+        <v>625177</v>
       </c>
       <c r="R15" t="n">
-        <v>7209530.9258211</v>
+        <v>7209552</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2022,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2051,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111396321</v>
+        <v>111396319</v>
       </c>
       <c r="B16" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,10 +2086,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>625240.2002264742</v>
+        <v>625229</v>
       </c>
       <c r="R16" t="n">
-        <v>7209649.650274927</v>
+        <v>7209608</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2119,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2148,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111396326</v>
+        <v>111396321</v>
       </c>
       <c r="B17" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,10 +2183,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625397.1584455093</v>
+        <v>625241</v>
       </c>
       <c r="R17" t="n">
-        <v>7209589.718691397</v>
+        <v>7209650</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2216,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,58 +2245,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111396308</v>
+        <v>111396322</v>
       </c>
       <c r="B18" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625151.1577179903</v>
+        <v>625269</v>
       </c>
       <c r="R18" t="n">
-        <v>7209567.512248591</v>
+        <v>7209630</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,19 +2313,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2587,15 +2342,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111396314</v>
+        <v>111396323</v>
       </c>
       <c r="B19" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2627,10 +2377,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>625202.8383709632</v>
+        <v>625302</v>
       </c>
       <c r="R19" t="n">
-        <v>7209539.171001118</v>
+        <v>7209611</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2660,19 +2410,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,55 +2439,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121561249</v>
+        <v>111396324</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625237</v>
+        <v>625336</v>
       </c>
       <c r="R20" t="n">
-        <v>7209648</v>
+        <v>7209609</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,12 +2504,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,55 +2536,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121561251</v>
+        <v>111396325</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625210</v>
+        <v>625390</v>
       </c>
       <c r="R21" t="n">
-        <v>7209469</v>
+        <v>7209581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2881,12 +2601,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,50 +2633,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121561250</v>
+        <v>111396326</v>
       </c>
       <c r="B22" t="n">
-        <v>57468</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gunnarn, Ly lm</t>
+          <t>V Lill-Tjickuträsket, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>625108</v>
+        <v>625397</v>
       </c>
       <c r="R22" t="n">
-        <v>7209511</v>
+        <v>7209590</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2983,12 +2698,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
